--- a/gu_in/Item.edf/26_TrapItem/TrapItem.xlsx
+++ b/gu_in/Item.edf/26_TrapItem/TrapItem.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A238C4-6C6E-4D9C-A8C1-EFE935422A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D903D4D6-BE03-45B1-B1A4-A006D3573D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TrapItem" sheetId="1" r:id="rId1"/>
@@ -737,7 +737,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -752,6 +752,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -788,12 +794,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,9 +822,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -852,9 +862,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -887,9 +897,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -922,9 +949,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1099,65 +1143,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BH55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="36" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="9" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="9" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1519,7 +1563,7 @@
       </c>
       <c r="BH2" s="2"/>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>63</v>
       </c>
@@ -1699,367 +1743,367 @@
       </c>
       <c r="BH3" s="2"/>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:60" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="5">
         <v>40</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="5">
         <v>40</v>
       </c>
-      <c r="J4" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K4" s="3">
-        <v>10</v>
-      </c>
-      <c r="L4" s="3">
-        <v>10</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
+      <c r="J4" s="5">
+        <v>-1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>10</v>
+      </c>
+      <c r="L4" s="5">
+        <v>10</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
         <v>60</v>
       </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2">
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="6">
         <v>25</v>
       </c>
-      <c r="Q4" s="2">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="3">
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
         <v>50</v>
       </c>
-      <c r="T4" s="2">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2">
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
         <v>299</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" s="6">
         <v>5501</v>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" s="6">
         <v>6080</v>
       </c>
-      <c r="X4" s="2">
+      <c r="X4" s="6">
         <v>40</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" s="6">
         <v>40</v>
       </c>
-      <c r="Z4" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="2">
+      <c r="Z4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="6">
         <v>1000</v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AC4" s="6">
         <v>0.5</v>
       </c>
-      <c r="AD4" s="2">
+      <c r="AD4" s="6">
         <v>0.5</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AE4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="AF4" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AL4" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AM4" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AN4" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AO4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AR4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="3">
+      <c r="AF4" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AG4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AL4" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AM4" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AN4" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AO4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="8">
+        <v>1363637</v>
+      </c>
+      <c r="AR4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="5">
         <v>75</v>
       </c>
-      <c r="AW4" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ4" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB4" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC4" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD4" s="2" t="s">
+      <c r="AW4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="5">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BE4" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BF4" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BG4" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH4" s="2"/>
+      <c r="BE4" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BF4" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BG4" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH4" s="6"/>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:60" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="5">
         <v>45</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="5">
         <v>45</v>
       </c>
-      <c r="J5" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K5" s="3">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3">
-        <v>10</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
+      <c r="J5" s="5">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>10</v>
+      </c>
+      <c r="L5" s="5">
+        <v>10</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6">
         <v>60</v>
       </c>
-      <c r="O5" s="3">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2">
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="6">
         <v>25</v>
       </c>
-      <c r="Q5" s="2">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3">
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
         <v>40</v>
       </c>
-      <c r="T5" s="2">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2">
+      <c r="T5" s="6">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6">
         <v>299</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5" s="6">
         <v>22116</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5" s="6">
         <v>24444</v>
       </c>
-      <c r="X5" s="2">
+      <c r="X5" s="6">
         <v>40</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y5" s="6">
         <v>50</v>
       </c>
-      <c r="Z5" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="2">
+      <c r="Z5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="6">
         <v>1000</v>
       </c>
-      <c r="AC5" s="2">
+      <c r="AC5" s="6">
         <v>0.5</v>
       </c>
-      <c r="AD5" s="2">
+      <c r="AD5" s="6">
         <v>0.5</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AE5" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="AF5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AL5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AM5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AN5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AO5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AR5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="3">
+      <c r="AF5" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AG5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AL5" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AM5" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AN5" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AO5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="8">
+        <v>2272728</v>
+      </c>
+      <c r="AR5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="5">
         <v>250</v>
       </c>
-      <c r="AW5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX5" s="3">
-        <v>1</v>
-      </c>
-      <c r="AY5" s="3">
-        <v>1</v>
-      </c>
-      <c r="AZ5" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA5" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC5" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD5" s="2" t="s">
+      <c r="AW5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA5" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BC5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BE5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BF5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BG5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH5" s="2"/>
+      <c r="BE5" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BF5" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BG5" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH5" s="6"/>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>71</v>
       </c>
@@ -2239,7 +2283,7 @@
       </c>
       <c r="BH6" s="2"/>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>73</v>
       </c>
@@ -2419,7 +2463,7 @@
       </c>
       <c r="BH7" s="2"/>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>75</v>
       </c>
@@ -2599,7 +2643,7 @@
       </c>
       <c r="BH8" s="2"/>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>77</v>
       </c>
@@ -2779,7 +2823,7 @@
       </c>
       <c r="BH9" s="2"/>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>79</v>
       </c>
@@ -2959,7 +3003,7 @@
       </c>
       <c r="BH10" s="2"/>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>81</v>
       </c>
@@ -3139,7 +3183,7 @@
       </c>
       <c r="BH11" s="2"/>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>83</v>
       </c>
@@ -3319,7 +3363,7 @@
       </c>
       <c r="BH12" s="2"/>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>85</v>
       </c>
@@ -3499,7 +3543,7 @@
       </c>
       <c r="BH13" s="2"/>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>88</v>
       </c>
@@ -3679,7 +3723,7 @@
       </c>
       <c r="BH14" s="2"/>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>90</v>
       </c>
@@ -3859,7 +3903,7 @@
       </c>
       <c r="BH15" s="2"/>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>92</v>
       </c>
@@ -4039,7 +4083,7 @@
       </c>
       <c r="BH16" s="2"/>
     </row>
-    <row r="17" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>94</v>
       </c>
@@ -4219,7 +4263,7 @@
       </c>
       <c r="BH17" s="2"/>
     </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>96</v>
       </c>
@@ -4399,7 +4443,7 @@
       </c>
       <c r="BH18" s="2"/>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>98</v>
       </c>
@@ -4579,7 +4623,7 @@
       </c>
       <c r="BH19" s="2"/>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>100</v>
       </c>
@@ -4759,7 +4803,7 @@
       </c>
       <c r="BH20" s="2"/>
     </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>102</v>
       </c>
@@ -4939,7 +4983,7 @@
       </c>
       <c r="BH21" s="2"/>
     </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>104</v>
       </c>
@@ -5119,7 +5163,7 @@
       </c>
       <c r="BH22" s="2"/>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
@@ -5299,7 +5343,7 @@
       </c>
       <c r="BH23" s="2"/>
     </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>109</v>
       </c>
@@ -5479,7 +5523,7 @@
       </c>
       <c r="BH24" s="2"/>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>111</v>
       </c>
@@ -5659,7 +5703,7 @@
       </c>
       <c r="BH25" s="2"/>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>113</v>
       </c>
@@ -5839,7 +5883,7 @@
       </c>
       <c r="BH26" s="2"/>
     </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>115</v>
       </c>
@@ -6019,7 +6063,7 @@
       </c>
       <c r="BH27" s="2"/>
     </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>117</v>
       </c>
@@ -6199,7 +6243,7 @@
       </c>
       <c r="BH28" s="2"/>
     </row>
-    <row r="29" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>119</v>
       </c>
@@ -6379,7 +6423,7 @@
       </c>
       <c r="BH29" s="2"/>
     </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>121</v>
       </c>
@@ -6559,7 +6603,7 @@
       </c>
       <c r="BH30" s="2"/>
     </row>
-    <row r="31" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>123</v>
       </c>
@@ -6739,7 +6783,7 @@
       </c>
       <c r="BH31" s="2"/>
     </row>
-    <row r="32" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>125</v>
       </c>
@@ -6919,7 +6963,7 @@
       </c>
       <c r="BH32" s="2"/>
     </row>
-    <row r="33" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>127</v>
       </c>
@@ -7099,7 +7143,7 @@
       </c>
       <c r="BH33" s="2"/>
     </row>
-    <row r="34" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>130</v>
       </c>
@@ -7279,7 +7323,7 @@
       </c>
       <c r="BH34" s="2"/>
     </row>
-    <row r="35" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>132</v>
       </c>
@@ -7459,7 +7503,7 @@
       </c>
       <c r="BH35" s="2"/>
     </row>
-    <row r="36" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>134</v>
       </c>
@@ -7639,7 +7683,7 @@
       </c>
       <c r="BH36" s="2"/>
     </row>
-    <row r="37" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>136</v>
       </c>
@@ -7819,7 +7863,7 @@
       </c>
       <c r="BH37" s="2"/>
     </row>
-    <row r="38" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>138</v>
       </c>
@@ -7999,7 +8043,7 @@
       </c>
       <c r="BH38" s="2"/>
     </row>
-    <row r="39" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>140</v>
       </c>
@@ -8179,7 +8223,7 @@
       </c>
       <c r="BH39" s="2"/>
     </row>
-    <row r="40" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>142</v>
       </c>
@@ -8359,7 +8403,7 @@
       </c>
       <c r="BH40" s="2"/>
     </row>
-    <row r="41" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>144</v>
       </c>
@@ -8539,7 +8583,7 @@
       </c>
       <c r="BH41" s="2"/>
     </row>
-    <row r="42" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>146</v>
       </c>
@@ -8719,7 +8763,7 @@
       </c>
       <c r="BH42" s="2"/>
     </row>
-    <row r="43" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>148</v>
       </c>
@@ -8899,7 +8943,7 @@
       </c>
       <c r="BH43" s="2"/>
     </row>
-    <row r="44" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>151</v>
       </c>
@@ -9079,7 +9123,7 @@
       </c>
       <c r="BH44" s="2"/>
     </row>
-    <row r="45" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>153</v>
       </c>
@@ -9259,7 +9303,7 @@
       </c>
       <c r="BH45" s="2"/>
     </row>
-    <row r="46" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>155</v>
       </c>
@@ -9439,7 +9483,7 @@
       </c>
       <c r="BH46" s="2"/>
     </row>
-    <row r="47" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>157</v>
       </c>
@@ -9619,7 +9663,7 @@
       </c>
       <c r="BH47" s="2"/>
     </row>
-    <row r="48" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>159</v>
       </c>
@@ -9799,7 +9843,7 @@
       </c>
       <c r="BH48" s="2"/>
     </row>
-    <row r="49" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>161</v>
       </c>
@@ -9979,7 +10023,7 @@
       </c>
       <c r="BH49" s="2"/>
     </row>
-    <row r="50" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>163</v>
       </c>
@@ -10159,7 +10203,7 @@
       </c>
       <c r="BH50" s="2"/>
     </row>
-    <row r="51" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>165</v>
       </c>
@@ -10339,7 +10383,7 @@
       </c>
       <c r="BH51" s="2"/>
     </row>
-    <row r="52" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>167</v>
       </c>
@@ -10519,7 +10563,7 @@
       </c>
       <c r="BH52" s="2"/>
     </row>
-    <row r="53" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>169</v>
       </c>
@@ -10699,7 +10743,7 @@
       </c>
       <c r="BH53" s="2"/>
     </row>
-    <row r="54" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>171</v>
       </c>
@@ -10879,7 +10923,7 @@
       </c>
       <c r="BH54" s="2"/>
     </row>
-    <row r="55" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>173</v>
       </c>
@@ -11068,46 +11112,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AJ55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="8" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>175</v>
       </c>
@@ -11217,7 +11261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>TrapItem!A2</f>
         <v>Code</v>
@@ -11351,7 +11395,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>TrapItem!A3</f>
         <v>tr00001</v>
@@ -11486,7 +11530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>TrapItem!A4</f>
         <v>tr00002</v>
@@ -11519,7 +11563,7 @@
       </c>
       <c r="I4">
         <f>TrapItem!AQ4</f>
-        <v>1500</v>
+        <v>1363637</v>
       </c>
       <c r="J4">
         <f>TrapItem!AR4</f>
@@ -11621,7 +11665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>TrapItem!A5</f>
         <v>tr00003</v>
@@ -11654,7 +11698,7 @@
       </c>
       <c r="I5">
         <f>TrapItem!AQ5</f>
-        <v>5000</v>
+        <v>2272728</v>
       </c>
       <c r="J5">
         <f>TrapItem!AR5</f>
@@ -11756,7 +11800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>TrapItem!A6</f>
         <v>tr00004</v>
@@ -11891,7 +11935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>TrapItem!A7</f>
         <v>tr00005</v>
@@ -12026,7 +12070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>TrapItem!A8</f>
         <v>tr00006</v>
@@ -12161,7 +12205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>TrapItem!A9</f>
         <v>tr00007</v>
@@ -12296,7 +12340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>TrapItem!A10</f>
         <v>tr00008</v>
@@ -12431,7 +12475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>TrapItem!A11</f>
         <v>tr00009</v>
@@ -12566,7 +12610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>TrapItem!A12</f>
         <v>tr00010</v>
@@ -12701,7 +12745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>TrapItem!A13</f>
         <v>tr00011</v>
@@ -12836,7 +12880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>TrapItem!A14</f>
         <v>tr00012</v>
@@ -12971,7 +13015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>TrapItem!A15</f>
         <v>tr00013</v>
@@ -13106,7 +13150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>TrapItem!A16</f>
         <v>tr00014</v>
@@ -13241,7 +13285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>TrapItem!A17</f>
         <v>tr00015</v>
@@ -13376,7 +13420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>TrapItem!A18</f>
         <v>tr00016</v>
@@ -13511,7 +13555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>TrapItem!A19</f>
         <v>tr00017</v>
@@ -13646,7 +13690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>TrapItem!A20</f>
         <v>tr00018</v>
@@ -13781,7 +13825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>TrapItem!A21</f>
         <v>tr00019</v>
@@ -13916,7 +13960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>TrapItem!A22</f>
         <v>tr00020</v>
@@ -14051,7 +14095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>TrapItem!A23</f>
         <v>tr00021</v>
@@ -14186,7 +14230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>TrapItem!A24</f>
         <v>tr00022</v>
@@ -14321,7 +14365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>TrapItem!A25</f>
         <v>tr00023</v>
@@ -14456,7 +14500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>TrapItem!A26</f>
         <v>tr00024</v>
@@ -14591,7 +14635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>TrapItem!A27</f>
         <v>tr00025</v>
@@ -14726,7 +14770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>TrapItem!A28</f>
         <v>tr00026</v>
@@ -14861,7 +14905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>TrapItem!A29</f>
         <v>tr00027</v>
@@ -14996,7 +15040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>TrapItem!A30</f>
         <v>tr00028</v>
@@ -15131,7 +15175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>TrapItem!A31</f>
         <v>tr00029</v>
@@ -15266,7 +15310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>TrapItem!A32</f>
         <v>tr00030</v>
@@ -15401,7 +15445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>TrapItem!A33</f>
         <v>tr00031</v>
@@ -15536,7 +15580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>TrapItem!A34</f>
         <v>tr00032</v>
@@ -15671,7 +15715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>TrapItem!A35</f>
         <v>tr00033</v>
@@ -15806,7 +15850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>TrapItem!A36</f>
         <v>tr00034</v>
@@ -15941,7 +15985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>TrapItem!A37</f>
         <v>tr00035</v>
@@ -16076,7 +16120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>TrapItem!A38</f>
         <v>tr00036</v>
@@ -16211,7 +16255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>TrapItem!A39</f>
         <v>tr00037</v>
@@ -16346,7 +16390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>TrapItem!A40</f>
         <v>tr00038</v>
@@ -16481,7 +16525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>TrapItem!A41</f>
         <v>tr00039</v>
@@ -16616,7 +16660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>TrapItem!A42</f>
         <v>tr00040</v>
@@ -16751,7 +16795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>TrapItem!A43</f>
         <v>tr00041</v>
@@ -16886,7 +16930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>TrapItem!A44</f>
         <v>tr00042</v>
@@ -17021,7 +17065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>TrapItem!A45</f>
         <v>tr00043</v>
@@ -17156,7 +17200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>TrapItem!A46</f>
         <v>tr00044</v>
@@ -17291,7 +17335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>TrapItem!A47</f>
         <v>tr00045</v>
@@ -17426,7 +17470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>TrapItem!A48</f>
         <v>tr00046</v>
@@ -17561,7 +17605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>TrapItem!A49</f>
         <v>tr00047</v>
@@ -17696,7 +17740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>TrapItem!A50</f>
         <v>tr00048</v>
@@ -17831,7 +17875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>TrapItem!A51</f>
         <v>tr00049</v>
@@ -17966,7 +18010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>TrapItem!A52</f>
         <v>tr00050</v>
@@ -18101,7 +18145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>TrapItem!A53</f>
         <v>trnew00</v>
@@ -18236,7 +18280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>TrapItem!A54</f>
         <v>trnew01</v>
@@ -18371,7 +18415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>TrapItem!A55</f>
         <v>trnew02</v>
@@ -18515,9 +18559,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -18528,7 +18572,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>181</v>
       </c>
@@ -18537,7 +18581,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>0</v>
       </c>
@@ -18546,7 +18590,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -18555,7 +18599,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -18564,7 +18608,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -18573,7 +18617,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -18582,7 +18626,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -18591,7 +18635,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -18600,7 +18644,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -18609,7 +18653,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -18618,7 +18662,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -18627,7 +18671,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -18636,7 +18680,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -18645,7 +18689,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -18654,7 +18698,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -18663,7 +18707,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -18672,7 +18716,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -18681,7 +18725,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -18690,7 +18734,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -18699,7 +18743,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -18708,7 +18752,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -18717,7 +18761,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -18726,7 +18770,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -18735,7 +18779,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -18744,7 +18788,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -18753,7 +18797,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -18762,7 +18806,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -18771,7 +18815,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -18780,7 +18824,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -18789,7 +18833,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -18798,7 +18842,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -18807,7 +18851,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -18816,7 +18860,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -18825,7 +18869,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -18834,7 +18878,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -18843,7 +18887,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -18852,7 +18896,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -18861,7 +18905,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -18870,7 +18914,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -18879,7 +18923,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -18888,7 +18932,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -18897,7 +18941,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -18906,7 +18950,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -18915,7 +18959,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -18924,7 +18968,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -18933,7 +18977,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -18942,7 +18986,7 @@
       </c>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -18951,7 +18995,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46</v>
       </c>
@@ -18960,7 +19004,7 @@
       </c>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47</v>
       </c>
@@ -18969,7 +19013,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -18978,7 +19022,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -18987,7 +19031,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>50</v>
       </c>
@@ -18996,7 +19040,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>51</v>
       </c>
@@ -19005,7 +19049,7 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>52</v>
       </c>

--- a/gu_in/Item.edf/26_TrapItem/TrapItem.xlsx
+++ b/gu_in/Item.edf/26_TrapItem/TrapItem.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D903D4D6-BE03-45B1-B1A4-A006D3573D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76745B30-2C17-4D05-B307-0A1721A41E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13725" yWindow="0" windowWidth="10110" windowHeight="11205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TrapItem" sheetId="1" r:id="rId1"/>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="AQ4" s="8">
-        <v>1363637</v>
+        <v>90910</v>
       </c>
       <c r="AR4" s="5">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="AQ5" s="8">
-        <v>2272728</v>
+        <v>136364</v>
       </c>
       <c r="AR5" s="5">
         <v>0</v>
@@ -11563,7 +11563,7 @@
       </c>
       <c r="I4">
         <f>TrapItem!AQ4</f>
-        <v>1363637</v>
+        <v>90910</v>
       </c>
       <c r="J4">
         <f>TrapItem!AR4</f>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="I5">
         <f>TrapItem!AQ5</f>
-        <v>2272728</v>
+        <v>136364</v>
       </c>
       <c r="J5">
         <f>TrapItem!AR5</f>
